--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.A. MONTEMAR.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.A. MONTEMAR.xlsx
@@ -643,13 +643,13 @@
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>11.043</v>
+        <v>3.5548</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7455000000000007</v>
+        <v>-2.7992</v>
       </c>
       <c r="F3" t="n">
-        <v>10.2975</v>
+        <v>6.354</v>
       </c>
       <c r="G3" t="n">
         <v>-14.2152</v>
@@ -688,13 +688,13 @@
         <v>29.6259</v>
       </c>
       <c r="S3" t="n">
-        <v>15.0615</v>
+        <v>7.5736</v>
       </c>
       <c r="T3" t="n">
-        <v>3.0814</v>
+        <v>-0.4631999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>11.9802</v>
+        <v>8.0366</v>
       </c>
       <c r="V3" t="n">
         <v>22.8395</v>
@@ -799,13 +799,13 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07030000000000008</v>
+        <v>-0.1532999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3085</v>
+        <v>-1.5034</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3789</v>
+        <v>1.3501</v>
       </c>
       <c r="G5" t="n">
         <v>-0.04979999999999984</v>
@@ -844,13 +844,13 @@
         <v>0.9435</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5655000000000001</v>
+        <v>0.3418</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1356</v>
+        <v>-0.05919999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4299</v>
+        <v>0.401</v>
       </c>
       <c r="V5" t="n">
         <v>-0.4453</v>
@@ -877,13 +877,13 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.889699999999999</v>
+        <v>-1.056000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>1.606999999999999</v>
+        <v>2.678700000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.4967</v>
+        <v>-3.7348</v>
       </c>
       <c r="G6" t="n">
         <v>3.158900000000001</v>
@@ -922,13 +922,13 @@
         <v>3.9627</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2158</v>
+        <v>1.0494</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.6526</v>
+        <v>-0.5808</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8684</v>
+        <v>1.6303</v>
       </c>
       <c r="V6" t="n">
         <v>-1.8678</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.5008</v>
+        <v>-2.2349</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.952</v>
+        <v>-1.6597</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5488</v>
+        <v>-0.5752</v>
       </c>
       <c r="G7" t="n">
         <v>-1.9272</v>
@@ -1000,13 +1000,13 @@
         <v>0.3774</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6302</v>
+        <v>-0.3643</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7642</v>
+        <v>-0.4719</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1341</v>
+        <v>0.1076</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3208</v>
@@ -1033,13 +1033,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>-9.2226</v>
+        <v>-8.7463</v>
       </c>
       <c r="E8" t="n">
         <v>-3.1087</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.1138</v>
+        <v>-5.6376</v>
       </c>
       <c r="G8" t="n">
         <v>-7.7437</v>
@@ -1078,13 +1078,13 @@
         <v>2.0757</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.0639</v>
+        <v>-2.5877</v>
       </c>
       <c r="T8" t="n">
         <v>-1.2904</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.7735</v>
+        <v>-1.2973</v>
       </c>
       <c r="V8" t="n">
         <v>0.6415999999999999</v>
@@ -1111,13 +1111,13 @@
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.562200000000001</v>
+        <v>-10.1891</v>
       </c>
       <c r="E9" t="n">
-        <v>-8.4878</v>
+        <v>-9.4033</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0744</v>
+        <v>-0.7857</v>
       </c>
       <c r="G9" t="n">
         <v>-6.5199</v>
@@ -1156,13 +1156,13 @@
         <v>2.8305</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7699</v>
+        <v>1.1431</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5089</v>
+        <v>0.5932999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2611</v>
+        <v>0.5498000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>2.1696</v>
@@ -1189,13 +1189,13 @@
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>-11.9166</v>
+        <v>-11.1565</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.9979</v>
+        <v>-4.6083</v>
       </c>
       <c r="F10" t="n">
-        <v>-6.9186</v>
+        <v>-6.5482</v>
       </c>
       <c r="G10" t="n">
         <v>-6.3011</v>
@@ -1234,13 +1234,13 @@
         <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.5589</v>
+        <v>-1.7988</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1634</v>
+        <v>-0.7737000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3954</v>
+        <v>-1.0251</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4904</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. TERREROS RIVAS</t>
+          <t>M. DAMESTOY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>-13.5427</v>
+        <v>-11.7957</v>
       </c>
       <c r="E11" t="n">
-        <v>7.109999999999999</v>
+        <v>-7.5467</v>
       </c>
       <c r="F11" t="n">
-        <v>-20.6527</v>
+        <v>-4.249</v>
       </c>
       <c r="G11" t="n">
-        <v>-11.836</v>
+        <v>-2.0265</v>
       </c>
       <c r="H11" t="n">
-        <v>-14.0734</v>
+        <v>-0.7756000000000003</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2372</v>
+        <v>-1.2509</v>
       </c>
       <c r="J11" t="n">
-        <v>25.2638</v>
+        <v>2.013</v>
       </c>
       <c r="K11" t="n">
-        <v>12.342</v>
+        <v>1.749</v>
       </c>
       <c r="L11" t="n">
-        <v>12.922</v>
+        <v>0.2637999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-37.09990000000001</v>
+        <v>-4.0395</v>
       </c>
       <c r="N11" t="n">
-        <v>-26.4151</v>
+        <v>-2.5246</v>
       </c>
       <c r="O11" t="n">
-        <v>-10.685</v>
+        <v>-1.5149</v>
       </c>
       <c r="P11" t="n">
-        <v>-10.3785</v>
+        <v>-4.340100000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-51.3264</v>
+        <v>-8.491499999999998</v>
       </c>
       <c r="R11" t="n">
-        <v>40.9479</v>
+        <v>4.1514</v>
       </c>
       <c r="S11" t="n">
-        <v>0.03470000000000012</v>
+        <v>-1.7315</v>
       </c>
       <c r="T11" t="n">
-        <v>6.911499999999999</v>
+        <v>-1.068</v>
       </c>
       <c r="U11" t="n">
-        <v>-6.8762</v>
+        <v>-0.6635</v>
       </c>
       <c r="V11" t="n">
-        <v>8.6371</v>
+        <v>-3.6976</v>
       </c>
       <c r="W11" t="n">
-        <v>26.261</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-17.6239</v>
+        <v>-3.6976</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. DAMESTOY</t>
+          <t>C. GILABERT FERRI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.6684</v>
+        <v>-17.0012</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.9694</v>
+        <v>-3.519000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.6987</v>
+        <v>-13.4819</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.0265</v>
+        <v>-12.3573</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7756000000000003</v>
+        <v>-15.3128</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2509</v>
+        <v>2.955499999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>2.013</v>
+        <v>8.6136</v>
       </c>
       <c r="K12" t="n">
-        <v>1.749</v>
+        <v>1.4627</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2637999999999999</v>
+        <v>7.1509</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.0395</v>
+        <v>-20.9711</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.5246</v>
+        <v>-16.7754</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.5149</v>
+        <v>-4.1957</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.340100000000001</v>
+        <v>-2.641800000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.491499999999998</v>
+        <v>-18.1152</v>
       </c>
       <c r="R12" t="n">
-        <v>4.1514</v>
+        <v>15.4734</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.604</v>
+        <v>-3.9192</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.4909</v>
+        <v>-3.6014</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.1133</v>
+        <v>-0.3175999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.6976</v>
+        <v>1.9172</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>9.5838</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.6976</v>
+        <v>-7.6666</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.459</v>
+        <v>-17.8234</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.444599999999999</v>
+        <v>-6.775399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.0144</v>
+        <v>-11.0479</v>
       </c>
       <c r="G13" t="n">
         <v>-14.3571</v>
@@ -1468,13 +1468,13 @@
         <v>4.1514</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4608</v>
+        <v>-1.8254</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7867999999999999</v>
+        <v>-1.1176</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6739999999999999</v>
+        <v>-0.7077</v>
       </c>
       <c r="V13" t="n">
         <v>-2.7732</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. GILABERT FERRI</t>
+          <t>B. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.8777</v>
+        <v>-19.8232</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.9825</v>
+        <v>-2.1226</v>
       </c>
       <c r="F14" t="n">
-        <v>-12.8955</v>
+        <v>-17.7</v>
       </c>
       <c r="G14" t="n">
-        <v>-12.3573</v>
+        <v>-11.836</v>
       </c>
       <c r="H14" t="n">
-        <v>-15.3128</v>
+        <v>-14.0734</v>
       </c>
       <c r="I14" t="n">
-        <v>2.955499999999999</v>
+        <v>2.2372</v>
       </c>
       <c r="J14" t="n">
-        <v>8.6136</v>
+        <v>25.2638</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4627</v>
+        <v>12.342</v>
       </c>
       <c r="L14" t="n">
-        <v>7.1509</v>
+        <v>12.922</v>
       </c>
       <c r="M14" t="n">
-        <v>-20.9711</v>
+        <v>-37.09990000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-16.7754</v>
+        <v>-26.4151</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.1957</v>
+        <v>-10.685</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.641800000000001</v>
+        <v>-10.3785</v>
       </c>
       <c r="Q14" t="n">
-        <v>-18.1152</v>
+        <v>-51.3264</v>
       </c>
       <c r="R14" t="n">
-        <v>15.4734</v>
+        <v>40.9479</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.7958</v>
+        <v>-6.2455</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.0646</v>
+        <v>-2.3216</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2689999999999999</v>
+        <v>-3.9239</v>
       </c>
       <c r="V14" t="n">
-        <v>1.9172</v>
+        <v>8.6371</v>
       </c>
       <c r="W14" t="n">
-        <v>9.5838</v>
+        <v>26.261</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.6666</v>
+        <v>-17.6239</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>-19.982</v>
+        <v>-21.5013</v>
       </c>
       <c r="E15" t="n">
-        <v>-13.3095</v>
+        <v>-15.0046</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.6724</v>
+        <v>-6.4967</v>
       </c>
       <c r="G15" t="n">
         <v>-4.585900000000001</v>
@@ -1624,13 +1624,13 @@
         <v>5.0949</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1598</v>
+        <v>-0.3594999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8796</v>
+        <v>0.1847</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.72</v>
+        <v>-0.5442</v>
       </c>
       <c r="V15" t="n">
         <v>-5.0454</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. GARCIA NAVEA</t>
+          <t>I. ALAMINOS HERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>-24.6301</v>
+        <v>-22.8513</v>
       </c>
       <c r="E16" t="n">
-        <v>-26.6067</v>
+        <v>-8.2721</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9765</v>
+        <v>-14.5793</v>
       </c>
       <c r="G16" t="n">
-        <v>-26.4561</v>
+        <v>-14.4171</v>
       </c>
       <c r="H16" t="n">
-        <v>-21.2008</v>
+        <v>-8.081900000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.2554</v>
+        <v>-6.335199999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>19.0903</v>
+        <v>0.7508</v>
       </c>
       <c r="K16" t="n">
-        <v>7.968899999999999</v>
+        <v>-0.07749999999999968</v>
       </c>
       <c r="L16" t="n">
-        <v>11.1214</v>
+        <v>0.8282999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-45.5467</v>
+        <v>-15.1679</v>
       </c>
       <c r="N16" t="n">
-        <v>-29.17</v>
+        <v>-8.004300000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>-16.3768</v>
+        <v>-7.1637</v>
       </c>
       <c r="P16" t="n">
-        <v>-53.4021</v>
+        <v>1.5096</v>
       </c>
       <c r="Q16" t="n">
-        <v>-96.42569999999999</v>
+        <v>-6.2271</v>
       </c>
       <c r="R16" t="n">
-        <v>43.0236</v>
+        <v>7.736700000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>11.5246</v>
+        <v>-3.748699999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1356</v>
+        <v>-2.4563</v>
       </c>
       <c r="U16" t="n">
-        <v>12.6603</v>
+        <v>-1.2923</v>
       </c>
       <c r="V16" t="n">
-        <v>43.7032</v>
+        <v>-6.195600000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>51.8636</v>
+        <v>-0.3397999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-8.160400000000001</v>
+        <v>-5.8558</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. ALAMINOS HERNANDEZ</t>
+          <t>M. MARTIN MARTINEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>-24.9656</v>
+        <v>-26.7899</v>
       </c>
       <c r="E17" t="n">
-        <v>-9.013200000000001</v>
+        <v>-15.8913</v>
       </c>
       <c r="F17" t="n">
-        <v>-15.9526</v>
+        <v>-10.8985</v>
       </c>
       <c r="G17" t="n">
-        <v>-14.4171</v>
+        <v>-13.6374</v>
       </c>
       <c r="H17" t="n">
-        <v>-8.081900000000001</v>
+        <v>-10.0278</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.335199999999999</v>
+        <v>-3.6093</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7508</v>
+        <v>5.8487</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.07749999999999968</v>
+        <v>4.1807</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8282999999999999</v>
+        <v>1.6679</v>
       </c>
       <c r="M17" t="n">
-        <v>-15.1679</v>
+        <v>-19.4857</v>
       </c>
       <c r="N17" t="n">
-        <v>-8.004300000000001</v>
+        <v>-14.2088</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.1637</v>
+        <v>-5.2777</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5096</v>
+        <v>-5.472300000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-6.2271</v>
+        <v>-26.9841</v>
       </c>
       <c r="R17" t="n">
-        <v>7.736700000000001</v>
+        <v>21.5118</v>
       </c>
       <c r="S17" t="n">
-        <v>-5.8626</v>
+        <v>-0.00219999999999998</v>
       </c>
       <c r="T17" t="n">
-        <v>-3.1972</v>
+        <v>-0.0007999999999998841</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.6657</v>
+        <v>-0.001900000000000179</v>
       </c>
       <c r="V17" t="n">
-        <v>-6.195600000000001</v>
+        <v>-7.678</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3397999999999999</v>
+        <v>5.2446</v>
       </c>
       <c r="X17" t="n">
-        <v>-5.8558</v>
+        <v>-12.9226</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MARTIN MARTINEZ</t>
+          <t>J. GARCIA NAVEA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>-25.8995</v>
+        <v>-34.4322</v>
       </c>
       <c r="E18" t="n">
-        <v>-12.7953</v>
+        <v>-29.8373</v>
       </c>
       <c r="F18" t="n">
-        <v>-13.1041</v>
+        <v>-4.595000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-13.6374</v>
+        <v>-26.4561</v>
       </c>
       <c r="H18" t="n">
-        <v>-10.0278</v>
+        <v>-21.2008</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.6093</v>
+        <v>-5.2554</v>
       </c>
       <c r="J18" t="n">
-        <v>5.8487</v>
+        <v>19.0903</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1807</v>
+        <v>7.968899999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6679</v>
+        <v>11.1214</v>
       </c>
       <c r="M18" t="n">
-        <v>-19.4857</v>
+        <v>-45.5467</v>
       </c>
       <c r="N18" t="n">
-        <v>-14.2088</v>
+        <v>-29.17</v>
       </c>
       <c r="O18" t="n">
-        <v>-5.2777</v>
+        <v>-16.3768</v>
       </c>
       <c r="P18" t="n">
-        <v>-5.472300000000001</v>
+        <v>-53.4021</v>
       </c>
       <c r="Q18" t="n">
-        <v>-26.9841</v>
+        <v>-96.42569999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>21.5118</v>
+        <v>43.0236</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8885000000000001</v>
+        <v>1.7227</v>
       </c>
       <c r="T18" t="n">
-        <v>3.0952</v>
+        <v>-4.3657</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.2071</v>
+        <v>6.0886</v>
       </c>
       <c r="V18" t="n">
-        <v>-7.678</v>
+        <v>43.7032</v>
       </c>
       <c r="W18" t="n">
-        <v>5.2446</v>
+        <v>51.8636</v>
       </c>
       <c r="X18" t="n">
-        <v>-12.9226</v>
+        <v>-8.160400000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>-42.8373</v>
+        <v>-41.1801</v>
       </c>
       <c r="E19" t="n">
-        <v>-16.8604</v>
+        <v>-17.151</v>
       </c>
       <c r="F19" t="n">
-        <v>-25.9773</v>
+        <v>-24.0289</v>
       </c>
       <c r="G19" t="n">
         <v>-23.4465</v>
@@ -1936,13 +1936,13 @@
         <v>18.1152</v>
       </c>
       <c r="S19" t="n">
-        <v>-10.7506</v>
+        <v>-9.0931</v>
       </c>
       <c r="T19" t="n">
-        <v>-4.2207</v>
+        <v>-4.5113</v>
       </c>
       <c r="U19" t="n">
-        <v>-6.530399999999999</v>
+        <v>-4.5821</v>
       </c>
       <c r="V19" t="n">
         <v>-9.5838</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. FERNANDEZ CARRASCO</t>
+          <t>G. GARCIA CARCASES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,76 +1966,76 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>-44.1585</v>
+        <v>-42.1155</v>
       </c>
       <c r="E20" t="n">
-        <v>-36.1249</v>
+        <v>-10.8035</v>
       </c>
       <c r="F20" t="n">
-        <v>-8.0335</v>
+        <v>-31.3122</v>
       </c>
       <c r="G20" t="n">
-        <v>-41.2823</v>
+        <v>-4.475300000000002</v>
       </c>
       <c r="H20" t="n">
-        <v>-19.8491</v>
+        <v>-5.878</v>
       </c>
       <c r="I20" t="n">
-        <v>-21.4335</v>
+        <v>1.4029</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.885699999999999</v>
+        <v>26.1846</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6004</v>
+        <v>13.0324</v>
       </c>
       <c r="L20" t="n">
-        <v>-10.4861</v>
+        <v>13.1522</v>
       </c>
       <c r="M20" t="n">
-        <v>-34.3966</v>
+        <v>-30.6599</v>
       </c>
       <c r="N20" t="n">
-        <v>-23.4491</v>
+        <v>-18.91</v>
       </c>
       <c r="O20" t="n">
-        <v>-10.9474</v>
+        <v>-11.7493</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3209</v>
+        <v>-13.5864</v>
       </c>
       <c r="Q20" t="n">
-        <v>-34.1547</v>
+        <v>-36.0417</v>
       </c>
       <c r="R20" t="n">
-        <v>35.4756</v>
+        <v>22.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.6882</v>
+        <v>-8.828900000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-4.6304</v>
+        <v>-7.436</v>
       </c>
       <c r="U20" t="n">
-        <v>1.9425</v>
+        <v>-1.3927</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.509</v>
+        <v>-15.2252</v>
       </c>
       <c r="W20" t="n">
-        <v>9.5458</v>
+        <v>6.489800000000001</v>
       </c>
       <c r="X20" t="n">
-        <v>-11.0548</v>
+        <v>-21.715</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. GARCIA CARCASES</t>
+          <t>M. FERNANDEZ CARRASCO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,70 +2044,70 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>-49.5807</v>
+        <v>-42.7271</v>
       </c>
       <c r="E21" t="n">
-        <v>-16.4377</v>
+        <v>-35.245</v>
       </c>
       <c r="F21" t="n">
-        <v>-33.1429</v>
+        <v>-7.482299999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.475300000000002</v>
+        <v>-41.2823</v>
       </c>
       <c r="H21" t="n">
-        <v>-5.878</v>
+        <v>-19.8491</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4029</v>
+        <v>-21.4335</v>
       </c>
       <c r="J21" t="n">
-        <v>26.1846</v>
+        <v>-6.885699999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>13.0324</v>
+        <v>3.6004</v>
       </c>
       <c r="L21" t="n">
-        <v>13.1522</v>
+        <v>-10.4861</v>
       </c>
       <c r="M21" t="n">
-        <v>-30.6599</v>
+        <v>-34.3966</v>
       </c>
       <c r="N21" t="n">
-        <v>-18.91</v>
+        <v>-23.4491</v>
       </c>
       <c r="O21" t="n">
-        <v>-11.7493</v>
+        <v>-10.9474</v>
       </c>
       <c r="P21" t="n">
-        <v>-13.5864</v>
+        <v>1.3209</v>
       </c>
       <c r="Q21" t="n">
-        <v>-36.0417</v>
+        <v>-34.1547</v>
       </c>
       <c r="R21" t="n">
-        <v>22.4553</v>
+        <v>35.4756</v>
       </c>
       <c r="S21" t="n">
-        <v>-16.2939</v>
+        <v>-1.2567</v>
       </c>
       <c r="T21" t="n">
-        <v>-13.0705</v>
+        <v>-3.7505</v>
       </c>
       <c r="U21" t="n">
-        <v>-3.2233</v>
+        <v>2.4937</v>
       </c>
       <c r="V21" t="n">
-        <v>-15.2252</v>
+        <v>-1.509</v>
       </c>
       <c r="W21" t="n">
-        <v>6.489800000000001</v>
+        <v>9.5458</v>
       </c>
       <c r="X21" t="n">
-        <v>-21.715</v>
+        <v>-11.0548</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>-58.7886</v>
+        <v>-47.2545</v>
       </c>
       <c r="E22" t="n">
-        <v>-36.9227</v>
+        <v>-30.899</v>
       </c>
       <c r="F22" t="n">
-        <v>-21.8656</v>
+        <v>-16.3556</v>
       </c>
       <c r="G22" t="n">
         <v>-24.7523</v>
@@ -2170,13 +2170,13 @@
         <v>22.8327</v>
       </c>
       <c r="S22" t="n">
-        <v>-22.4982</v>
+        <v>-10.9642</v>
       </c>
       <c r="T22" t="n">
-        <v>-13.7077</v>
+        <v>-7.6837</v>
       </c>
       <c r="U22" t="n">
-        <v>-8.790700000000001</v>
+        <v>-3.2806</v>
       </c>
       <c r="V22" t="n">
         <v>-10.0284</v>
@@ -2203,13 +2203,13 @@
         <v>21</v>
       </c>
       <c r="D23" t="n">
-        <v>-111.5106</v>
+        <v>-95.2316</v>
       </c>
       <c r="E23" t="n">
-        <v>-85.5742</v>
+        <v>-75.6718</v>
       </c>
       <c r="F23" t="n">
-        <v>-25.9361</v>
+        <v>-19.56</v>
       </c>
       <c r="G23" t="n">
         <v>-52.5612</v>
@@ -2248,13 +2248,13 @@
         <v>36.4191</v>
       </c>
       <c r="S23" t="n">
-        <v>-28.0517</v>
+        <v>-11.7729</v>
       </c>
       <c r="T23" t="n">
-        <v>-18.3003</v>
+        <v>-8.3977</v>
       </c>
       <c r="U23" t="n">
-        <v>-9.751300000000001</v>
+        <v>-3.3751</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0831</v>
@@ -2281,13 +2281,13 @@
         <v>24</v>
       </c>
       <c r="D24" t="n">
-        <v>-464.2463999999999</v>
+        <v>-445.8754</v>
       </c>
       <c r="E24" t="n">
-        <v>-259.8006</v>
+        <v>-254.5103</v>
       </c>
       <c r="F24" t="n">
-        <v>-204.4452</v>
+        <v>-191.3647</v>
       </c>
       <c r="G24" t="n">
         <v>-255.1561</v>
@@ -2302,7 +2302,7 @@
         <v>103.3952</v>
       </c>
       <c r="K24" t="n">
-        <v>68.39609999999999</v>
+        <v>68.3961</v>
       </c>
       <c r="L24" t="n">
         <v>34.99890000000001</v>
@@ -2326,13 +2326,13 @@
         <v>318.903</v>
       </c>
       <c r="S24" t="n">
-        <v>-71.0385</v>
+        <v>-52.668</v>
       </c>
       <c r="T24" t="n">
-        <v>-54.8631</v>
+        <v>-49.5718</v>
       </c>
       <c r="U24" t="n">
-        <v>-16.1754</v>
+        <v>-3.096399999999999</v>
       </c>
       <c r="V24" t="n">
         <v>11.9646</v>
